--- a/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/KennysSimplified.xlsx
+++ b/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/KennysSimplified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://defra-my.sharepoint.com/personal/william_skalka_defra_gov_uk/Documents/Documents/GitHub/ea-wigan-waste-transfer-notes/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{8D328007-643D-4387-B249-36E45171352B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{149790EF-06F3-4BFD-B5B8-5BF215C6E8D8}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{8D328007-643D-4387-B249-36E45171352B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F3E06A-DCE8-4B68-8513-8D0192EC644B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3D87BFF-B695-4E3E-B3C1-CE00A55FE5AF}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{C3D87BFF-B695-4E3E-B3C1-CE00A55FE5AF}"/>
   </bookViews>
   <sheets>
     <sheet name="WTN Spreadsheet" sheetId="1" r:id="rId1"/>
@@ -36,39 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Net Weight</t>
-  </si>
-  <si>
-    <t>Name of Site</t>
-  </si>
-  <si>
-    <t>Haulier</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Ref Number</t>
-  </si>
-  <si>
-    <t>Ref Description</t>
-  </si>
-  <si>
-    <t>EWC</t>
-  </si>
-  <si>
-    <t>Material Description</t>
-  </si>
-  <si>
     <t>Vehicle Reg</t>
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Ticket Reference</t>
+  </si>
+  <si>
+    <t>Waste Type</t>
+  </si>
+  <si>
+    <t>Net Tonnage</t>
+  </si>
+  <si>
+    <t>Carrier Name</t>
+  </si>
+  <si>
+    <t>Carrier Licence</t>
+  </si>
+  <si>
+    <t>Carrier (Other)</t>
+  </si>
+  <si>
+    <t>Broker</t>
+  </si>
+  <si>
+    <t>Receiving Site Details</t>
+  </si>
+  <si>
+    <t>Receiving Site Authorisation</t>
   </si>
 </sst>
 </file>
@@ -443,46 +446,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9203B69-372D-4B20-9ECB-6DAFF3DA2CC7}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
+      <c r="L1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
